--- a/output/cars.xlsx
+++ b/output/cars.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-05-25T02:09:54.378652+00:00</t>
+          <t>2026-05-25T02:13:42.266981+00:00</t>
         </is>
       </c>
     </row>
